--- a/sampleprojects/TestProject/excel/Test.xlsx
+++ b/sampleprojects/TestProject/excel/Test.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Test Entry Point" sheetId="2" r:id="rId4"/>
+    <sheet name="EDD" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>DT: Test Entry Point</t>
   </si>
@@ -61,6 +62,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>thing.value == 2</t>
   </si>
   <si>
@@ -92,13 +96,100 @@
   </si>
   <si>
     <t>thing.value is out of range, i.e.  {thing.value}</t>
+  </si>
+  <si>
+    <t>EDD: EDD</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SubType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>(2 attributes)</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Notes on processing the job</t>
+  </si>
+  <si>
+    <t>things</t>
+  </si>
+  <si>
+    <t>This test tests things</t>
+  </si>
+  <si>
+    <t>thing</t>
+  </si>
+  <si>
+    <t>(1 attributes)</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,8 +215,45 @@
       <color/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0070C0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF00B050"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFED7D31"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,6 +268,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD0D0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0D8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFC0"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
@@ -185,6 +328,39 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,13 +903,13 @@
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>6</v>
@@ -780,19 +956,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>6</v>
@@ -839,19 +1015,19 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>6</v>
@@ -898,19 +1074,19 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>6</v>
@@ -951,11 +1127,11 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1014,19 +1190,19 @@
         <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>6</v>
@@ -1067,11 +1243,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -1186,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>6</v>
@@ -1245,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>6</v>
@@ -1304,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>6</v>
@@ -1375,4 +1551,233 @@
     <mergeCell ref="A21:B21"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="18"/>
+    <col customWidth="true" max="2" min="2" width="25"/>
+    <col customWidth="true" max="3" min="3" width="10"/>
+    <col customWidth="true" max="4" min="4" width="12"/>
+    <col customWidth="true" max="5" min="5" width="18"/>
+    <col customWidth="true" max="7" min="6" width="8"/>
+    <col customWidth="true" max="8" min="8" width="55"/>
+    <col customWidth="true" max="9" min="9" width="8"/>
+    <col customWidth="true" max="10" min="10" width="30"/>
+    <col customWidth="true" max="11" min="11" width="16"/>
+    <col customWidth="true" max="12" min="12" width="30"/>
+    <col customWidth="true" max="13" min="13" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>